--- a/outputs/unpatched_ann_grid.xlsx
+++ b/outputs/unpatched_ann_grid.xlsx
@@ -476,20 +476,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.782866910099983</v>
+        <v>5.50665371119976</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9938503593368969</v>
+        <v>1.034068434070141</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9690348982810975</v>
+        <v>0.9612958550453186</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02043911821068023</v>
+        <v>0.02656126428804035</v>
       </c>
     </row>
     <row r="3">
@@ -503,20 +503,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.816980883479118</v>
+        <v>5.640318691730499</v>
       </c>
       <c r="E3" t="n">
-        <v>1.253126896110832</v>
+        <v>1.152904912195762</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9683208346366883</v>
+        <v>0.9575774550437928</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02647662838946208</v>
+        <v>0.02346370756159655</v>
       </c>
     </row>
     <row r="4">
@@ -530,20 +530,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.015451945364475</v>
+        <v>5.780973434448242</v>
       </c>
       <c r="E4" t="n">
-        <v>1.614482039942419</v>
+        <v>1.070723210766899</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9699641823768616</v>
+        <v>0.9521645069122314</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01741903731308592</v>
+        <v>0.03076388009495369</v>
       </c>
     </row>
     <row r="5">
@@ -557,20 +557,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.119224786758423</v>
+        <v>5.90051680803299</v>
       </c>
       <c r="E5" t="n">
-        <v>1.830456832696435</v>
+        <v>1.770259567731462</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9648540735244751</v>
+        <v>0.9527002453804017</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02769114022239381</v>
+        <v>0.03390856544537157</v>
       </c>
     </row>
     <row r="6">
@@ -584,20 +584,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5.139940716326237</v>
+        <v>5.924487411975861</v>
       </c>
       <c r="E6" t="n">
-        <v>1.645400103193869</v>
+        <v>1.458038585570786</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9618404150009155</v>
+        <v>0.951429295539856</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0313601753033708</v>
+        <v>0.03025003713232196</v>
       </c>
     </row>
     <row r="7">
@@ -611,20 +611,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.256057344377041</v>
+        <v>5.961481779813766</v>
       </c>
       <c r="E7" t="n">
-        <v>1.905788144229434</v>
+        <v>1.261883682082291</v>
       </c>
       <c r="F7" t="n">
-        <v>0.953877854347229</v>
+        <v>0.9452078223228455</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03213596474438223</v>
+        <v>0.04711577368614275</v>
       </c>
     </row>
     <row r="8">
@@ -638,20 +638,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.285005643963814</v>
+        <v>6.217490583658218</v>
       </c>
       <c r="E8" t="n">
-        <v>2.542293912000506</v>
+        <v>1.190048222539151</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9549591541290283</v>
+        <v>0.9421149611473083</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04176659644529655</v>
+        <v>0.03589994121327282</v>
       </c>
     </row>
     <row r="9">
@@ -665,20 +665,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.326892994344234</v>
+        <v>6.492022126913071</v>
       </c>
       <c r="E9" t="n">
-        <v>2.309781985974117</v>
+        <v>1.494057233936337</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9584339261054993</v>
+        <v>0.9492428064346313</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02784351870531096</v>
+        <v>0.02784754560149493</v>
       </c>
     </row>
     <row r="10">
@@ -692,20 +692,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5.362526811659336</v>
+        <v>6.524828523397446</v>
       </c>
       <c r="E10" t="n">
-        <v>1.815672230224645</v>
+        <v>1.565476972776844</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9656142830848694</v>
+        <v>0.9475290179252625</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02518017637028598</v>
+        <v>0.03423353549148182</v>
       </c>
     </row>
     <row r="11">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.393654592335224</v>
+        <v>6.632690355181694</v>
       </c>
       <c r="E11" t="n">
-        <v>2.442450435012594</v>
+        <v>1.755025746944123</v>
       </c>
       <c r="F11" t="n">
-        <v>0.955994701385498</v>
+        <v>0.9465335965156555</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0396651627008837</v>
+        <v>0.02301774144036346</v>
       </c>
     </row>
     <row r="12">
@@ -746,20 +746,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5.407735593616962</v>
+        <v>6.666989848017693</v>
       </c>
       <c r="E12" t="n">
-        <v>1.928225329199953</v>
+        <v>1.704876321591726</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9552194476127625</v>
+        <v>0.9434340238571167</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03361729631523584</v>
+        <v>0.02652755949965933</v>
       </c>
     </row>
     <row r="13">
@@ -773,20 +773,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5.512292049825191</v>
+        <v>6.717895865440369</v>
       </c>
       <c r="E13" t="n">
-        <v>2.314468752314253</v>
+        <v>1.737102959945265</v>
       </c>
       <c r="F13" t="n">
-        <v>0.955816388130188</v>
+        <v>0.94048672914505</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02916109354873933</v>
+        <v>0.03176939909076333</v>
       </c>
     </row>
     <row r="14">
@@ -800,20 +800,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5.608198381960392</v>
+        <v>6.74177311360836</v>
       </c>
       <c r="E14" t="n">
-        <v>2.471196543032108</v>
+        <v>2.235041234654103</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9559101104736328</v>
+        <v>0.9300442576408386</v>
       </c>
       <c r="G14" t="n">
-        <v>0.03385498918208237</v>
+        <v>0.0469824309358675</v>
       </c>
     </row>
     <row r="15">
@@ -827,20 +827,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.718377530574799</v>
+        <v>6.787012740969658</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9135242008192225</v>
+        <v>1.597101739112367</v>
       </c>
       <c r="F15" t="n">
-        <v>0.948194682598114</v>
+        <v>0.9432553291320801</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03828937955684879</v>
+        <v>0.03663828716865566</v>
       </c>
     </row>
     <row r="16">
@@ -854,20 +854,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.740262381732464</v>
+        <v>6.818801090121269</v>
       </c>
       <c r="E16" t="n">
-        <v>2.192377981473521</v>
+        <v>2.187827427810285</v>
       </c>
       <c r="F16" t="n">
-        <v>0.95082026720047</v>
+        <v>0.9338300466537476</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03437381710178105</v>
+        <v>0.04920025315796138</v>
       </c>
     </row>
     <row r="17">
@@ -881,20 +881,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5.846507847309113</v>
+        <v>6.89887747168541</v>
       </c>
       <c r="E17" t="n">
-        <v>1.93566720125329</v>
+        <v>1.722571531915536</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9626391768455506</v>
+        <v>0.9386795878410339</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02362896955108583</v>
+        <v>0.03646236225425867</v>
       </c>
     </row>
     <row r="18">
@@ -908,20 +908,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5.853546522557735</v>
+        <v>7.016028612852097</v>
       </c>
       <c r="E18" t="n">
-        <v>2.416785570105366</v>
+        <v>2.098190125683114</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9563320398330688</v>
+        <v>0.9308850884437561</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03423612250527276</v>
+        <v>0.03923562077287737</v>
       </c>
     </row>
     <row r="19">
@@ -935,20 +935,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5.883816294372082</v>
+        <v>7.153329253196716</v>
       </c>
       <c r="E19" t="n">
-        <v>2.595382324682367</v>
+        <v>1.635793952437218</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9559612989425659</v>
+        <v>0.9365772366523742</v>
       </c>
       <c r="G19" t="n">
-        <v>0.02495985978839165</v>
+        <v>0.03815314469721666</v>
       </c>
     </row>
     <row r="20">
@@ -962,20 +962,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6.15920402109623</v>
+        <v>7.187610939145088</v>
       </c>
       <c r="E20" t="n">
-        <v>2.780155003045991</v>
+        <v>1.250570484117068</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9595120668411254</v>
+        <v>0.9449093818664551</v>
       </c>
       <c r="G20" t="n">
-        <v>0.02974948770953758</v>
+        <v>0.03335817000227454</v>
       </c>
     </row>
     <row r="21">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6.545683071017265</v>
+        <v>7.198473885655403</v>
       </c>
       <c r="E21" t="n">
-        <v>2.442995084790516</v>
+        <v>1.716726321937138</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9508798360824585</v>
+        <v>0.9426293253898621</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02743787610872827</v>
+        <v>0.03606000416515968</v>
       </c>
     </row>
     <row r="22">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7.515418827533722</v>
+        <v>7.835819497704506</v>
       </c>
       <c r="E22" t="n">
-        <v>2.530251855093786</v>
+        <v>2.310663611852126</v>
       </c>
       <c r="F22" t="n">
-        <v>0.942306923866272</v>
+        <v>0.9153546690940857</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0365568973167946</v>
+        <v>0.04305560836049246</v>
       </c>
     </row>
     <row r="23">
@@ -1043,20 +1043,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7.603145688772202</v>
+        <v>8.091798052191734</v>
       </c>
       <c r="E23" t="n">
-        <v>3.217642648714869</v>
+        <v>2.780191682361731</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9416366219520569</v>
+        <v>0.9047032952308655</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03833411175506806</v>
+        <v>0.05857815643821652</v>
       </c>
     </row>
     <row r="24">
@@ -1070,20 +1070,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7.638242170214653</v>
+        <v>8.213370442390442</v>
       </c>
       <c r="E24" t="n">
-        <v>3.170285855809935</v>
+        <v>2.770025773026465</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9303500533103943</v>
+        <v>0.912663733959198</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03664668054534168</v>
+        <v>0.04306141976446252</v>
       </c>
     </row>
     <row r="25">
@@ -1097,20 +1097,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7.649224996566772</v>
+        <v>8.275810778141022</v>
       </c>
       <c r="E25" t="n">
-        <v>3.205092814651442</v>
+        <v>2.169636939577213</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9411697149276733</v>
+        <v>0.9129591345787048</v>
       </c>
       <c r="G25" t="n">
-        <v>0.03792079992686134</v>
+        <v>0.04140048695330537</v>
       </c>
     </row>
     <row r="26">
@@ -1124,20 +1124,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7.825166508555412</v>
+        <v>8.343108370900154</v>
       </c>
       <c r="E26" t="n">
-        <v>3.532065776487122</v>
+        <v>2.070429262966892</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9432760596275329</v>
+        <v>0.9116542100906372</v>
       </c>
       <c r="G26" t="n">
-        <v>0.04202581690484467</v>
+        <v>0.0484689588752058</v>
       </c>
     </row>
     <row r="27">
@@ -1151,20 +1151,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8.013728559017181</v>
+        <v>8.779680356383324</v>
       </c>
       <c r="E27" t="n">
-        <v>2.592639667085117</v>
+        <v>2.316519428312722</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9497461676597595</v>
+        <v>0.9023252725601196</v>
       </c>
       <c r="G27" t="n">
-        <v>0.02773655097863584</v>
+        <v>0.0552180138966674</v>
       </c>
     </row>
     <row r="28">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8.035150095820427</v>
+        <v>8.811095654964447</v>
       </c>
       <c r="E28" t="n">
-        <v>4.887808188813858</v>
+        <v>1.324948881825239</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9314346551895142</v>
+        <v>0.9109225630760193</v>
       </c>
       <c r="G28" t="n">
-        <v>0.05927331522006938</v>
+        <v>0.03481170301999695</v>
       </c>
     </row>
     <row r="29">
@@ -1205,20 +1205,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8.049855679273605</v>
+        <v>8.849419355392456</v>
       </c>
       <c r="E29" t="n">
-        <v>3.549223425376839</v>
+        <v>2.098537458628567</v>
       </c>
       <c r="F29" t="n">
-        <v>0.941627812385559</v>
+        <v>0.9002526521682739</v>
       </c>
       <c r="G29" t="n">
-        <v>0.04332258890309011</v>
+        <v>0.05988717759739468</v>
       </c>
     </row>
     <row r="30">
@@ -1232,20 +1232,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>8.102120757102966</v>
+        <v>8.863004595041275</v>
       </c>
       <c r="E30" t="n">
-        <v>4.503384337671496</v>
+        <v>2.269251503317926</v>
       </c>
       <c r="F30" t="n">
-        <v>0.926363718509674</v>
+        <v>0.9047391057014466</v>
       </c>
       <c r="G30" t="n">
-        <v>0.06050333212706484</v>
+        <v>0.06204252285252516</v>
       </c>
     </row>
     <row r="31">
@@ -1259,20 +1259,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.141273632645607</v>
+        <v>8.98267462849617</v>
       </c>
       <c r="E31" t="n">
-        <v>2.360406869479864</v>
+        <v>2.632625460063363</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9458651900291443</v>
+        <v>0.9010227918624878</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02564280235372455</v>
+        <v>0.04942386414529083</v>
       </c>
     </row>
     <row r="32">
@@ -1286,20 +1286,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8.315906003117561</v>
+        <v>9.047123938798904</v>
       </c>
       <c r="E32" t="n">
-        <v>2.567187741381979</v>
+        <v>2.323450594726486</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9384339809417724</v>
+        <v>0.8992295026779175</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0369179931622664</v>
+        <v>0.06188133431165516</v>
       </c>
     </row>
     <row r="33">
@@ -1313,20 +1313,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>8.365459591150284</v>
+        <v>9.105471298098564</v>
       </c>
       <c r="E33" t="n">
-        <v>3.369626293663592</v>
+        <v>2.44936404015884</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9406421542167663</v>
+        <v>0.8937487363815307</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04386796361100191</v>
+        <v>0.07128461417599867</v>
       </c>
     </row>
     <row r="34">
@@ -1340,20 +1340,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>8.377880752086639</v>
+        <v>9.117620289325714</v>
       </c>
       <c r="E34" t="n">
-        <v>2.617876600251932</v>
+        <v>2.500878391608261</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8906713366508484</v>
+        <v>0.9009859323501587</v>
       </c>
       <c r="G34" t="n">
-        <v>0.09639123311256619</v>
+        <v>0.0637240638387495</v>
       </c>
     </row>
     <row r="35">
@@ -1367,20 +1367,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>8.416044637560844</v>
+        <v>9.166926890611649</v>
       </c>
       <c r="E35" t="n">
-        <v>4.859624881689947</v>
+        <v>2.329071644200221</v>
       </c>
       <c r="F35" t="n">
-        <v>0.92561936378479</v>
+        <v>0.9011556267738342</v>
       </c>
       <c r="G35" t="n">
-        <v>0.07486199143457715</v>
+        <v>0.05615198599776356</v>
       </c>
     </row>
     <row r="36">
@@ -1394,20 +1394,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.43106709420681</v>
+        <v>9.261789545416832</v>
       </c>
       <c r="E36" t="n">
-        <v>3.577790174950939</v>
+        <v>2.088065239576141</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9468420267105102</v>
+        <v>0.8997485637664795</v>
       </c>
       <c r="G36" t="n">
-        <v>0.03296473979527084</v>
+        <v>0.04388415816998422</v>
       </c>
     </row>
     <row r="37">
@@ -1425,16 +1425,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8.54909211397171</v>
+        <v>9.27982285618782</v>
       </c>
       <c r="E37" t="n">
-        <v>3.102428345528724</v>
+        <v>1.530339245729274</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8910308361053467</v>
+        <v>0.8732430934906006</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1002540137760385</v>
+        <v>0.1158752772544542</v>
       </c>
     </row>
     <row r="38">
@@ -1448,20 +1448,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8.560394793748856</v>
+        <v>9.304680153727531</v>
       </c>
       <c r="E38" t="n">
-        <v>5.06653511639431</v>
+        <v>3.10058565150685</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9211503624916076</v>
+        <v>0.894688856601715</v>
       </c>
       <c r="G38" t="n">
-        <v>0.08675281439147101</v>
+        <v>0.06954988128295814</v>
       </c>
     </row>
     <row r="39">
@@ -1475,20 +1475,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8.725060820579529</v>
+        <v>9.558940082788467</v>
       </c>
       <c r="E39" t="n">
-        <v>4.553228870532234</v>
+        <v>2.306046287255586</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9275112390518189</v>
+        <v>0.8898603439331054</v>
       </c>
       <c r="G39" t="n">
-        <v>0.05522471870604277</v>
+        <v>0.07135551167956704</v>
       </c>
     </row>
     <row r="40">
@@ -1502,20 +1502,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8.818384483456612</v>
+        <v>9.605599045753479</v>
       </c>
       <c r="E40" t="n">
-        <v>3.260347756283567</v>
+        <v>2.350756992602456</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9182369112968445</v>
+        <v>0.8887346386909485</v>
       </c>
       <c r="G40" t="n">
-        <v>0.04055873766110502</v>
+        <v>0.06981290456108825</v>
       </c>
     </row>
     <row r="41">
@@ -1529,20 +1529,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8.914362713694572</v>
+        <v>9.85627293586731</v>
       </c>
       <c r="E41" t="n">
-        <v>4.772686585607411</v>
+        <v>2.018784590314806</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9217795252799987</v>
+        <v>0.888806962966919</v>
       </c>
       <c r="G41" t="n">
-        <v>0.07466787267664061</v>
+        <v>0.06183673303124346</v>
       </c>
     </row>
     <row r="42">
@@ -1556,20 +1556,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9.101362749934196</v>
+        <v>9.857692271471024</v>
       </c>
       <c r="E42" t="n">
-        <v>4.481201497900447</v>
+        <v>2.802772935917928</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9327507257461548</v>
+        <v>0.8861305832862854</v>
       </c>
       <c r="G42" t="n">
-        <v>0.05290118337013553</v>
+        <v>0.07150176017936721</v>
       </c>
     </row>
     <row r="43">
@@ -1583,20 +1583,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>9.282395914196968</v>
+        <v>9.878486767411232</v>
       </c>
       <c r="E43" t="n">
-        <v>4.349648377062304</v>
+        <v>2.824805973598751</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9220166325569152</v>
+        <v>0.8489822149276733</v>
       </c>
       <c r="G43" t="n">
-        <v>0.05761042109258963</v>
+        <v>0.09714831135874989</v>
       </c>
     </row>
     <row r="44">
@@ -1610,20 +1610,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>9.380817785859108</v>
+        <v>9.932973980903625</v>
       </c>
       <c r="E44" t="n">
-        <v>3.783157261461371</v>
+        <v>2.564575881215616</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8898111939430237</v>
+        <v>0.8430720210075379</v>
       </c>
       <c r="G44" t="n">
-        <v>0.08824699333502925</v>
+        <v>0.135216356721198</v>
       </c>
     </row>
     <row r="45">
@@ -1637,20 +1637,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.0418334454298</v>
+        <v>10.2447597682476</v>
       </c>
       <c r="E45" t="n">
-        <v>3.050089668475285</v>
+        <v>1.616198606548454</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8884872198104858</v>
+        <v>0.8614335536956788</v>
       </c>
       <c r="G45" t="n">
-        <v>0.08357055847393464</v>
+        <v>0.08705508624945271</v>
       </c>
     </row>
     <row r="46">
@@ -1668,16 +1668,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.04232138395309</v>
+        <v>10.75894698500633</v>
       </c>
       <c r="E46" t="n">
-        <v>2.428188562120639</v>
+        <v>3.958304922226807</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7552256345748901</v>
+        <v>0.8006073951721191</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1976844023840033</v>
+        <v>0.1725018307769849</v>
       </c>
     </row>
     <row r="47">
@@ -1691,20 +1691,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.25932446122169</v>
+        <v>10.91784730553627</v>
       </c>
       <c r="E47" t="n">
-        <v>1.899857738170673</v>
+        <v>2.187483388579762</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7572998881340027</v>
+        <v>0.8522172331809997</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1608279259236283</v>
+        <v>0.06869955634912682</v>
       </c>
     </row>
     <row r="48">
@@ -1718,20 +1718,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>44.56011742353439</v>
+        <v>11.07795678079128</v>
       </c>
       <c r="E48" t="n">
-        <v>16.53828874626423</v>
+        <v>5.637193850920977</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.2818889379501343</v>
+        <v>0.79597989320755</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4253231965491649</v>
+        <v>0.2195875838236394</v>
       </c>
     </row>
     <row r="49">
@@ -1745,20 +1745,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>44.7474279999733</v>
+        <v>30.24241879582405</v>
       </c>
       <c r="E49" t="n">
-        <v>16.83025230975592</v>
+        <v>16.74024249387064</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.3230811595916748</v>
+        <v>0.2025382041931152</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4239149639771049</v>
+        <v>0.509957473663012</v>
       </c>
     </row>
     <row r="50">
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>44.76057022809982</v>
+        <v>46.17955267429352</v>
       </c>
       <c r="E50" t="n">
-        <v>16.71525286154597</v>
+        <v>10.83720537040873</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.2763402462005615</v>
+        <v>-0.1536699056625366</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4299319483790596</v>
+        <v>0.1704842315462392</v>
       </c>
     </row>
     <row r="51">
@@ -1803,16 +1803,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>45.04330635070801</v>
+        <v>46.72514021396637</v>
       </c>
       <c r="E51" t="n">
-        <v>16.50977939482123</v>
+        <v>11.15957945826675</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2697826385498047</v>
+        <v>-0.1608327150344849</v>
       </c>
       <c r="G51" t="n">
-        <v>0.4318451074572773</v>
+        <v>0.1568756043580084</v>
       </c>
     </row>
   </sheetData>
